--- a/clino_hkk_plane_hkl.xlsx
+++ b/clino_hkk_plane_hkl.xlsx
@@ -489,7 +489,7 @@
         <v>139.4091139313641</v>
       </c>
       <c r="E2" t="n">
-        <v>-134.7509626812379</v>
+        <v>-134.7507488783882</v>
       </c>
       <c r="F2" t="n">
         <v>-20.38790312912558</v>
@@ -500,7 +500,7 @@
       <c r="H2" t="n">
         <v>13</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -518,7 +518,7 @@
         <v>102.2915322990421</v>
       </c>
       <c r="E3" t="n">
-        <v>-124.3500536146398</v>
+        <v>-124.3500687846745</v>
       </c>
       <c r="F3" t="n">
         <v>-20.38790312912558</v>
@@ -529,7 +529,7 @@
       <c r="H3" t="n">
         <v>13</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -547,7 +547,7 @@
         <v>82.16928863455162</v>
       </c>
       <c r="E4" t="n">
-        <v>-109.4186747075971</v>
+        <v>-109.4188077319088</v>
       </c>
       <c r="F4" t="n">
         <v>-20.38790312912558</v>
@@ -558,7 +558,7 @@
       <c r="H4" t="n">
         <v>13</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -576,7 +576,7 @@
         <v>73.26036889899578</v>
       </c>
       <c r="E5" t="n">
-        <v>-89.77021653932633</v>
+        <v>-89.76726634631321</v>
       </c>
       <c r="F5" t="n">
         <v>-20.38790312912558</v>
@@ -587,7 +587,7 @@
       <c r="H5" t="n">
         <v>13</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -605,7 +605,7 @@
         <v>75.96922092903665</v>
       </c>
       <c r="E6" t="n">
-        <v>-68.72237043436748</v>
+        <v>-68.72243982064303</v>
       </c>
       <c r="F6" t="n">
         <v>-20.38790312912558</v>
@@ -616,7 +616,7 @@
       <c r="H6" t="n">
         <v>13</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -634,7 +634,7 @@
         <v>90.02824703161372</v>
       </c>
       <c r="E7" t="n">
-        <v>-51.08893160831467</v>
+        <v>-51.08782837323725</v>
       </c>
       <c r="F7" t="n">
         <v>-20.38790312912558</v>
@@ -645,7 +645,7 @@
       <c r="H7" t="n">
         <v>13</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -663,7 +663,7 @@
         <v>116.1539996575274</v>
       </c>
       <c r="E8" t="n">
-        <v>-38.40027959681209</v>
+        <v>-38.3984008038007</v>
       </c>
       <c r="F8" t="n">
         <v>-20.38790312912558</v>
@@ -674,7 +674,7 @@
       <c r="H8" t="n">
         <v>13</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -692,7 +692,7 @@
         <v>108.1034567372476</v>
       </c>
       <c r="E9" t="n">
-        <v>-144.7500862457275</v>
+        <v>-144.7530912414512</v>
       </c>
       <c r="F9" t="n">
         <v>-20.38790312912558</v>
@@ -703,7 +703,7 @@
       <c r="H9" t="n">
         <v>13</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>77.40514313451853</v>
       </c>
       <c r="E10" t="n">
-        <v>-134.7535261277876</v>
+        <v>-134.7508054945594</v>
       </c>
       <c r="F10" t="n">
         <v>-20.38790312912558</v>
@@ -732,7 +732,7 @@
       <c r="H10" t="n">
         <v>13</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v>56.66804921342927</v>
       </c>
       <c r="E11" t="n">
-        <v>-117.5196771021928</v>
+        <v>-117.5203926778931</v>
       </c>
       <c r="F11" t="n">
         <v>-20.38790312912558</v>
@@ -761,7 +761,7 @@
       <c r="H11" t="n">
         <v>13</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -779,7 +779,7 @@
         <v>46.87708320459633</v>
       </c>
       <c r="E12" t="n">
-        <v>-89.76658513296843</v>
+        <v>-89.76737327826037</v>
       </c>
       <c r="F12" t="n">
         <v>-20.38790312912558</v>
@@ -790,7 +790,7 @@
       <c r="H12" t="n">
         <v>13</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -808,7 +808,7 @@
         <v>51.66294231248899</v>
       </c>
       <c r="E13" t="n">
-        <v>-59.28912003981984</v>
+        <v>-59.28868178850383</v>
       </c>
       <c r="F13" t="n">
         <v>-20.38790312912558</v>
@@ -819,7 +819,7 @@
       <c r="H13" t="n">
         <v>13</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -837,7 +837,7 @@
         <v>68.92123816560994</v>
       </c>
       <c r="E14" t="n">
-        <v>-38.40011136521984</v>
+        <v>-38.39990479515156</v>
       </c>
       <c r="F14" t="n">
         <v>-20.38790312912558</v>
@@ -848,7 +848,7 @@
       <c r="H14" t="n">
         <v>13</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -866,7 +866,7 @@
         <v>95.64363387837386</v>
       </c>
       <c r="E15" t="n">
-        <v>-26.29826809591996</v>
+        <v>-26.29826809592175</v>
       </c>
       <c r="F15" t="n">
         <v>-20.38790312912558</v>
@@ -877,7 +877,7 @@
       <c r="H15" t="n">
         <v>13</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -895,7 +895,7 @@
         <v>91.16374885469629</v>
       </c>
       <c r="E16" t="n">
-        <v>-157.9345654918076</v>
+        <v>-157.934429916563</v>
       </c>
       <c r="F16" t="n">
         <v>-20.38790312912558</v>
@@ -906,7 +906,7 @@
       <c r="H16" t="n">
         <v>13</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -924,7 +924,7 @@
         <v>60.60812886432331</v>
       </c>
       <c r="E17" t="n">
-        <v>-150.9293198444163</v>
+        <v>-150.9293198444157</v>
       </c>
       <c r="F17" t="n">
         <v>-20.38790312912558</v>
@@ -935,7 +935,7 @@
       <c r="H17" t="n">
         <v>13</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -953,7 +953,7 @@
         <v>36.43666303084053</v>
       </c>
       <c r="E18" t="n">
-        <v>-134.7511016602875</v>
+        <v>-134.75110165973</v>
       </c>
       <c r="F18" t="n">
         <v>-20.38790312912558</v>
@@ -964,7 +964,7 @@
       <c r="H18" t="n">
         <v>13</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -982,7 +982,7 @@
         <v>22.94324557192664</v>
       </c>
       <c r="E19" t="n">
-        <v>-89.76714416408036</v>
+        <v>-89.76714416408225</v>
       </c>
       <c r="F19" t="n">
         <v>-20.38790312912558</v>
@@ -993,7 +993,7 @@
       <c r="H19" t="n">
         <v>13</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
         <v>32.86909367224321</v>
       </c>
       <c r="E20" t="n">
-        <v>-38.39975099456563</v>
+        <v>-38.39975099456569</v>
       </c>
       <c r="F20" t="n">
         <v>-20.38790312912558</v>
@@ -1022,7 +1022,7 @@
       <c r="H20" t="n">
         <v>13</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
         <v>55.83501608398304</v>
       </c>
       <c r="E21" t="n">
-        <v>-19.02027837354871</v>
+        <v>-19.020278373549</v>
       </c>
       <c r="F21" t="n">
         <v>-20.38790312912558</v>
@@ -1051,7 +1051,7 @@
       <c r="H21" t="n">
         <v>13</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         <v>85.07298799447561</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.03824946031066</v>
+        <v>-11.03824946031063</v>
       </c>
       <c r="F22" t="n">
         <v>-20.38790312912558</v>
@@ -1080,7 +1080,7 @@
       <c r="H22" t="n">
         <v>13</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
         <v>83.57532188013604</v>
       </c>
       <c r="E23" t="n">
-        <v>-1254.018669586444</v>
+        <v>-1254.018669594668</v>
       </c>
       <c r="F23" t="n">
         <v>-20.38790312912558</v>
@@ -1109,7 +1109,7 @@
       <c r="H23" t="n">
         <v>13</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         <v>52.75046453934014</v>
       </c>
       <c r="E24" t="n">
-        <v>-1254.018710038113</v>
+        <v>-1254.018710102524</v>
       </c>
       <c r="F24" t="n">
         <v>-20.38790312912558</v>
@@ -1138,7 +1138,7 @@
       <c r="H24" t="n">
         <v>13</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
         <v>25.6676293802924</v>
       </c>
       <c r="E25" t="n">
-        <v>-1254.018784834078</v>
+        <v>-1254.018784958005</v>
       </c>
       <c r="F25" t="n">
         <v>-20.38790312912558</v>
@@ -1167,7 +1167,7 @@
       <c r="H25" t="n">
         <v>13</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       <c r="H26" t="n">
         <v>13</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         <v>25.6676293802924</v>
       </c>
       <c r="E27" t="n">
-        <v>5.981178253552143</v>
+        <v>5.981178253548852</v>
       </c>
       <c r="F27" t="n">
         <v>-20.38790312912558</v>
@@ -1225,7 +1225,7 @@
       <c r="H27" t="n">
         <v>13</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
         <v>52.75046453934014</v>
       </c>
       <c r="E28" t="n">
-        <v>5.981270925156059</v>
+        <v>5.981270925153707</v>
       </c>
       <c r="F28" t="n">
         <v>-20.38790312912558</v>
@@ -1254,7 +1254,7 @@
       <c r="H28" t="n">
         <v>13</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>83.57532188013604</v>
       </c>
       <c r="E29" t="n">
-        <v>5.981319640492675</v>
+        <v>5.981319640491081</v>
       </c>
       <c r="F29" t="n">
         <v>-20.38790312912558</v>
@@ -1283,7 +1283,7 @@
       <c r="H29" t="n">
         <v>13</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
         <v>85.07298799447561</v>
       </c>
       <c r="E30" t="n">
-        <v>528.9617615523165</v>
+        <v>528.9617615522252</v>
       </c>
       <c r="F30" t="n">
         <v>-20.38790312912558</v>
@@ -1312,7 +1312,7 @@
       <c r="H30" t="n">
         <v>13</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
         <v>55.83501608398304</v>
       </c>
       <c r="E31" t="n">
-        <v>6640.979744828254</v>
+        <v>6640.979744895829</v>
       </c>
       <c r="F31" t="n">
         <v>-20.38790312912558</v>
@@ -1341,7 +1341,7 @@
       <c r="H31" t="n">
         <v>13</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
         <v>32.86909367224321</v>
       </c>
       <c r="E32" t="n">
-        <v>141.6001818117453</v>
+        <v>141.600181811748</v>
       </c>
       <c r="F32" t="n">
         <v>-20.38790312912558</v>
@@ -1370,7 +1370,7 @@
       <c r="H32" t="n">
         <v>13</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
         <v>22.94324557192664</v>
       </c>
       <c r="E33" t="n">
-        <v>90.23277612673138</v>
+        <v>90.23277612673209</v>
       </c>
       <c r="F33" t="n">
         <v>-20.38790312912558</v>
@@ -1399,7 +1399,7 @@
       <c r="H33" t="n">
         <v>13</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
         <v>36.43666303084053</v>
       </c>
       <c r="E34" t="n">
-        <v>45.24890494865145</v>
+        <v>45.24890494864778</v>
       </c>
       <c r="F34" t="n">
         <v>-20.38790312912558</v>
@@ -1428,7 +1428,7 @@
       <c r="H34" t="n">
         <v>13</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
         <v>60.60812886432331</v>
       </c>
       <c r="E35" t="n">
-        <v>29.07068387597142</v>
+        <v>29.07068387596629</v>
       </c>
       <c r="F35" t="n">
         <v>-20.38790312912558</v>
@@ -1457,7 +1457,7 @@
       <c r="H35" t="n">
         <v>13</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
         <v>91.16374885469629</v>
       </c>
       <c r="E36" t="n">
-        <v>22.0655059913864</v>
+        <v>22.04628077550482</v>
       </c>
       <c r="F36" t="n">
         <v>-20.38790312912558</v>
@@ -1486,7 +1486,7 @@
       <c r="H36" t="n">
         <v>13</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
         <v>95.64363387837386</v>
       </c>
       <c r="E37" t="n">
-        <v>153.7017003024982</v>
+        <v>153.7017003025089</v>
       </c>
       <c r="F37" t="n">
         <v>-20.38790312912558</v>
@@ -1515,7 +1515,7 @@
       <c r="H37" t="n">
         <v>13</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         <v>68.92123816560994</v>
       </c>
       <c r="E38" t="n">
-        <v>141.6002579182134</v>
+        <v>141.6002105480288</v>
       </c>
       <c r="F38" t="n">
         <v>-20.38790312912558</v>
@@ -1544,7 +1544,7 @@
       <c r="H38" t="n">
         <v>13</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
         <v>51.66294231248899</v>
       </c>
       <c r="E39" t="n">
-        <v>120.7114728723496</v>
+        <v>120.7115691715481</v>
       </c>
       <c r="F39" t="n">
         <v>-20.38790312912558</v>
@@ -1573,7 +1573,7 @@
       <c r="H39" t="n">
         <v>13</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
         <v>46.87708320459633</v>
       </c>
       <c r="E40" t="n">
-        <v>90.23281099547503</v>
+        <v>90.23284074285245</v>
       </c>
       <c r="F40" t="n">
         <v>-20.38790312912558</v>
@@ -1602,7 +1602,7 @@
       <c r="H40" t="n">
         <v>13</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         <v>56.66804921342927</v>
       </c>
       <c r="E41" t="n">
-        <v>62.47996820447087</v>
+        <v>62.47996345879105</v>
       </c>
       <c r="F41" t="n">
         <v>-20.38790312912558</v>
@@ -1631,7 +1631,7 @@
       <c r="H41" t="n">
         <v>13</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>77.40514313451853</v>
       </c>
       <c r="E42" t="n">
-        <v>45.24863404789218</v>
+        <v>45.24889131428485</v>
       </c>
       <c r="F42" t="n">
         <v>-20.38790312912558</v>
@@ -1660,7 +1660,7 @@
       <c r="H42" t="n">
         <v>13</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
         <v>108.1034567372476</v>
       </c>
       <c r="E43" t="n">
-        <v>35.24744994768259</v>
+        <v>35.2477133397208</v>
       </c>
       <c r="F43" t="n">
         <v>-20.38790312912558</v>
@@ -1689,7 +1689,7 @@
       <c r="H43" t="n">
         <v>13</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
         <v>116.1539996575274</v>
       </c>
       <c r="E44" t="n">
-        <v>141.6000655172684</v>
+        <v>141.6005227784194</v>
       </c>
       <c r="F44" t="n">
         <v>-20.38790312912558</v>
@@ -1718,7 +1718,7 @@
       <c r="H44" t="n">
         <v>13</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>90.02824703161372</v>
       </c>
       <c r="E45" t="n">
-        <v>128.9109477900824</v>
+        <v>128.9110846177238</v>
       </c>
       <c r="F45" t="n">
         <v>-20.38790312912558</v>
@@ -1747,7 +1747,7 @@
       <c r="H45" t="n">
         <v>13</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
         <v>75.96922092903665</v>
       </c>
       <c r="E46" t="n">
-        <v>111.2784249973011</v>
+        <v>111.2775924385365</v>
       </c>
       <c r="F46" t="n">
         <v>-20.38790312912558</v>
@@ -1776,7 +1776,7 @@
       <c r="H46" t="n">
         <v>13</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         <v>73.26036889899578</v>
       </c>
       <c r="E47" t="n">
-        <v>90.23903667712645</v>
+        <v>90.23288563351387</v>
       </c>
       <c r="F47" t="n">
         <v>-20.38790312912558</v>
@@ -1805,7 +1805,7 @@
       <c r="H47" t="n">
         <v>13</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
         <v>82.16928863455162</v>
       </c>
       <c r="E48" t="n">
-        <v>70.58155483797648</v>
+        <v>70.58141735373472</v>
       </c>
       <c r="F48" t="n">
         <v>-20.38790312912558</v>
@@ -1834,7 +1834,7 @@
       <c r="H48" t="n">
         <v>13</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
         <v>102.2915322990421</v>
       </c>
       <c r="E49" t="n">
-        <v>55.64993532834261</v>
+        <v>55.64986822578127</v>
       </c>
       <c r="F49" t="n">
         <v>-20.38790312912558</v>
@@ -1863,7 +1863,7 @@
       <c r="H49" t="n">
         <v>13</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
         <v>139.4091139313641</v>
       </c>
       <c r="E50" t="n">
-        <v>45.24895978369636</v>
+        <v>45.24879553048981</v>
       </c>
       <c r="F50" t="n">
         <v>-20.38790312912558</v>
@@ -1892,7 +1892,7 @@
       <c r="H50" t="n">
         <v>13</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50" t="b">
         <v>0</v>
       </c>
     </row>
